--- a/diagnostico_fondos.xlsx
+++ b/diagnostico_fondos.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LTV y Leverage estan en grafico de barras (numeros no asociables de forma confiable a la columna vigente); Rentabilidad 12M / Dividend Yield / TIR son sobre valor libro, no bursatil.</t>
+          <t>Rentabilidad 12M / Dividend Yield / TIR son sobre valor libro, no bursatil. LTV leido de las etiquetas de dato del grafico 'Loan to Value Total (LTV)' (por posicion, no por orden de lectura del texto). Leverage esta en un grafico cuya unica linea es 'Tasa promedio deuda financiera' (no Leverage en si) -&gt; se deja vacio para no cargar el dato equivocado.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1515,32 +1515,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No (la rentabilidad esta en grafico, no en texto/tabla, o el informe no la incluye)</t>
+          <t>Parcial (se extrajeron algunos campos pero no todos)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>E. Rentabilidad en grafico / tabla no estandar (no extraible por regex)</t>
+          <t>F. Rentabilidad extraida parcialmente</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>Rentabilidad extraida parcialmente (mencion suelta en texto libre)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Rentabilidad 'Desde Inicio' leida del texto libre del comentario (UF), no de una tabla.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Construir un agente que lea el grafico (ejes/leyenda) o pida el dato en formato tabla a la administradora.</t>
+          <t>Revisar el PDF y completar manualmente los campos faltantes, o ajustar el regex del agente.</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. El PDF menciona una rentabilidad OBJETIVO (no realizada) de UF+6,4% para el aportante; no se carga en ninguna columna para no confundirla con un resultado medido.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica. El PDF menciona una formula contractual de rentabilidad objetivo (UF+8,0% anual, Distribucion Extraordinaria), no un resultado medido; no se carga en ninguna columna.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sitio caido durante el re-scrapeo (assetagf.com no respondio)</t>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos (documento incorrecto, sin datos de rentabilidad). Reintentar navegando a la pestaña especifica de cada fondo en https://assetagf.com/fondos-de-inversion/ | El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos Asset (documento incorrecto, sin datos de rentabilidad).</t>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py. | El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos Asset (documento incorrecto, sin datos de rentabilidad).</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sitio caido durante el re-scrapeo (assetagf.com no respondio)</t>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos (documento incorrecto, sin datos de rentabilidad). Reintentar navegando a la pestaña especifica de cada fondo en https://assetagf.com/fondos-de-inversion/ | El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos Asset (documento incorrecto, sin datos de rentabilidad).</t>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py. | El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos Asset (documento incorrecto, sin datos de rentabilidad).</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sitio caido durante el re-scrapeo (assetagf.com no respondio)</t>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos (documento incorrecto, sin datos de rentabilidad). Reintentar navegando a la pestaña especifica de cada fondo en https://assetagf.com/fondos-de-inversion/ | El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos Asset (documento incorrecto, sin datos de rentabilidad).</t>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py. | El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos Asset (documento incorrecto, sin datos de rentabilidad).</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">

--- a/diagnostico_fondos.xlsx
+++ b/diagnostico_fondos.xlsx
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aconcagua III</t>
+          <t>Renta Residencial II</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-CC-IA-III.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-IN-CC-RR-II.aspx</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1567,42 +1567,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260508_Aconcagua III.pdf</t>
+          <t>20260508_Renta Residencial II.pdf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Si (revisar)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No (la rentabilidad esta en grafico, no en texto/tabla, o el informe no la incluye)</t>
+          <t>Parcial / sin clasificar automaticamente</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>E. Rentabilidad en grafico / tabla no estandar (no extraible por regex)</t>
+          <t>F. Rentabilidad extraida parcialmente</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>Rentabilidad calculada desde Valor Cuota (Inicio vs Actual)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Calculado desde Valor Cuota: 27.280,54 el 29-08-2018 -&gt; 33.885,00 el 30-09-2025. Es variacion de PRECIO de la cuota solamente (no incluye dividendos repartidos en el camino) y no esta anualizada -- no es directamente comparable con 'Desde Inicio' de otras administradoras, que si suele incluir dividendos.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Construir un agente que lea el grafico (ejes/leyenda) o pida el dato en formato tabla a la administradora.</t>
+          <t>Revisar el PDF y completar manualmente los campos faltantes, o ajustar el regex del agente.</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital Raíces</t>
+          <t>Renta Residencial III</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-IC-CR.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/credicorp-capital-renta-residencial-iii.aspx</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1629,42 +1629,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260825_FIX_FactSheet.pdf</t>
+          <t>20260508_Renta Residencial III.pdf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Si (revisar)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No (la rentabilidad esta en grafico, no en texto/tabla, o el informe no la incluye)</t>
+          <t>Parcial / sin clasificar automaticamente</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>E. Rentabilidad en grafico / tabla no estandar (no extraible por regex)</t>
+          <t>F. Rentabilidad extraida parcialmente</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>Rentabilidad calculada desde Valor Cuota (Inicio vs Actual)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Calculado desde Valor Cuota: 33.401,71 el 10-08-2022 -&gt; 39.147,70 el 30-09-2025. Es variacion de PRECIO de la cuota solamente (no incluye dividendos repartidos en el camino) y no esta anualizada -- no es directamente comparable con 'Desde Inicio' de otras administradoras, que si suele incluir dividendos.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Construir un agente que lea el grafico (ejes/leyenda) o pida el dato en formato tabla a la administradora.</t>
+          <t>Revisar el PDF y completar manualmente los campos faltantes, o ajustar el regex del agente.</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Plaza Egaña</t>
+          <t>Aconcagua III</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-CC-PE.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-CC-IA-III.aspx</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260508_Plaza Egaña.pdf</t>
+          <t>20260508_Aconcagua III.pdf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Preferente Maestra II</t>
+          <t>Capital Raíces</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-CC-M-II.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-IC-CR.aspx</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Renta Industrial I</t>
+          <t>Plaza Egaña</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/cc-patio-renta-industrial-i.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-CC-PE.aspx</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260508_Renta Industrial I.pdf</t>
+          <t>20260508_Plaza Egaña.pdf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Renta Inmobiliaria II</t>
+          <t>Preferente Maestra II</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FFIIRIII.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-CC-M-II.aspx</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260508_Renta Inmobiliaria II.pdf</t>
+          <t>20260825_FIX_FactSheet.pdf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Renta Residencial I</t>
+          <t>Renta Industrial I</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-IN-CC-RR-I.aspx?t=1</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/cc-patio-renta-industrial-i.aspx</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260508_Renta Residencial I.pdf</t>
+          <t>20260508_Renta Industrial I.pdf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Renta Residencial II</t>
+          <t>Renta Inmobiliaria II</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-IN-CC-RR-II.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FFIIRIII.aspx</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260508_Renta Residencial II.pdf</t>
+          <t>20260508_Renta Inmobiliaria II.pdf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Renta Residencial III</t>
+          <t>Renta Residencial I</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/credicorp-capital-renta-residencial-iii.aspx</t>
+          <t>https://www.credicorpcapital.com/Chile/Neg/GestAct/Paginas/FF-II-IN-CC-RR-I.aspx?t=1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260508_Renta Residencial III.pdf</t>
+          <t>20260508_Renta Residencial I.pdf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
